--- a/ExcelDataTest/Shopee_Product_Variation_Sales_Report.xlsx
+++ b/ExcelDataTest/Shopee_Product_Variation_Sales_Report.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Education\PlatformSale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PlatformSale\ExcelDataTest\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3134E10-A718-45BF-A86C-C3F3C58B92E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -642,8 +642,6 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -652,6 +650,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1392,14 +1392,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="3" spans="1:9" ht="15">
       <c r="A3" s="1" t="s">
@@ -1438,10 +1438,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="23.25" customHeight="1">
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="11">
         <v>3348</v>
       </c>
     </row>
@@ -1464,488 +1464,488 @@
       <c r="F7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="11">
         <v>1188</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="28.5">
-      <c r="A8" s="10">
+      <c r="A8" s="8">
         <v>1</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="8">
         <v>3348</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="8">
         <v>3328</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>670</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.5">
-      <c r="A9" s="10">
+      <c r="A9" s="8">
         <v>2</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <v>1188</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <v>1187</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="11">
         <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="28.5">
-      <c r="A10" s="10">
+      <c r="A10" s="8">
         <v>3</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="8">
         <v>670</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="8">
         <v>665</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="11">
         <v>587</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="28.5">
-      <c r="A11" s="10">
+      <c r="A11" s="8">
         <v>4</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="8">
         <v>616</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <v>614</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="11">
         <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="28.5">
-      <c r="A12" s="10">
+      <c r="A12" s="8">
         <v>5</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="8">
         <v>587</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="8">
         <v>581</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="11">
         <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.5">
-      <c r="A13" s="10">
+      <c r="A13" s="8">
         <v>6</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="8">
         <v>350</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <v>343</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="11">
         <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="28.5">
-      <c r="A14" s="10">
+      <c r="A14" s="8">
         <v>7</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="8">
         <v>215</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <v>213</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="12" t="s">
+      <c r="H14" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>132</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="10">
+      <c r="A15" s="8">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="8">
         <v>187</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <v>187</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="11">
         <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="28.5">
-      <c r="A16" s="10">
+      <c r="A16" s="8">
         <v>9</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>132</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="8">
         <v>132</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="11">
         <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="10">
+      <c r="A17" s="8">
         <v>10</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="8">
         <v>126</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="8">
         <v>126</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="11">
         <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.5">
-      <c r="A18" s="10">
+      <c r="A18" s="8">
         <v>11</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>93</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="8">
         <v>92</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="11">
         <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="10">
+      <c r="A19" s="8">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="8">
         <v>87</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <v>87</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="11">
         <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="10">
+      <c r="A20" s="8">
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="8">
         <v>77</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="8">
         <v>77</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="11">
         <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="28.5">
-      <c r="A21" s="10">
+      <c r="A21" s="8">
         <v>14</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>77</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="8">
         <v>77</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="28.5">
-      <c r="A22" s="10">
+      <c r="A22" s="8">
         <v>15</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="8">
         <v>77</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="8">
         <v>77</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="28.5">
-      <c r="A23" s="10">
+      <c r="A23" s="8">
         <v>16</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="8">
         <v>76</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="8">
         <v>73</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="F23" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="28.5">
-      <c r="A24" s="10">
+      <c r="A24" s="8">
         <v>17</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="8">
         <v>69</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="8">
         <v>61</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="28.5">
-      <c r="A25" s="10">
+      <c r="A25" s="8">
         <v>18</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="8">
         <v>67</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="8">
         <v>67</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="10">
+      <c r="A26" s="8">
         <v>19</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <v>67</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <v>64</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="10">
+      <c r="A27" s="8">
         <v>20</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <v>66</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <v>66</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="9" t="s">
         <v>74</v>
       </c>
     </row>
@@ -2009,1940 +2009,1940 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="28.5">
-      <c r="A2" s="10">
+      <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="8">
         <v>3348</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <v>3328</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="8">
         <v>3328</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="8">
         <v>7161522</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="8">
         <v>2200</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="8">
         <v>2900</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="8">
         <v>979</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="8">
         <v>2900</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="28.5">
-      <c r="A3" s="10">
+      <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="8">
         <v>1188</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="8">
         <v>1187</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="8">
         <v>1187</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>4520957</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>3900</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="8">
         <v>5000</v>
       </c>
-      <c r="J3" s="10">
+      <c r="J3" s="8">
         <v>3000</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="8">
         <v>5000</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="28.5">
-      <c r="A4" s="10">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="8">
         <v>670</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="8">
         <v>665</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="8">
         <v>665</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>151250</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>390</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="8">
         <v>390</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="8">
         <v>198</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="8">
         <v>390</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="28.5">
-      <c r="A5" s="10">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>616</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>614</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>614</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>290616</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>690</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <v>690</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="8">
         <v>315</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="8">
         <v>490</v>
       </c>
-      <c r="L5" s="11" t="s">
+      <c r="L5" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="28.5">
-      <c r="A6" s="10">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="10">
+      <c r="D6" s="8">
         <v>587</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="8">
         <v>581</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="8">
         <v>581</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="8">
         <v>578643</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>1290</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="8">
         <v>1290</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="8">
         <v>863</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="8">
         <v>1040</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="L6" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="28.5">
-      <c r="A7" s="10">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="8">
         <v>350</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="8">
         <v>343</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="8">
         <v>343</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="8">
         <v>237107</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>1080</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="8">
         <v>1080</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="8">
         <v>415</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="8">
         <v>690</v>
       </c>
-      <c r="L7" s="11" t="s">
+      <c r="L7" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="28.5">
-      <c r="A8" s="10">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="8">
         <v>215</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="8">
         <v>213</v>
       </c>
-      <c r="F8" s="10">
+      <c r="F8" s="8">
         <v>213</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="8">
         <v>186369</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <v>1380</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="8">
         <v>1380</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J8" s="8">
         <v>801</v>
       </c>
-      <c r="K8" s="10">
+      <c r="K8" s="8">
         <v>1380</v>
       </c>
-      <c r="L8" s="11" t="s">
+      <c r="L8" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="10">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="8">
         <v>187</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="8">
         <v>187</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="8">
         <v>187</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>1500</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>500</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="8">
         <v>500</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="8">
         <v>0</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="8">
         <v>500</v>
       </c>
-      <c r="L9" s="11" t="s">
+      <c r="L9" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="28.5">
-      <c r="A10" s="10">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="8">
         <v>132</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="8">
         <v>132</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="8">
         <v>132</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="8">
         <v>55440</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>780</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="8">
         <v>780</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="8">
         <v>420</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="8">
         <v>420</v>
       </c>
-      <c r="L10" s="11" t="s">
+      <c r="L10" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="10">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="8">
         <v>126</v>
       </c>
-      <c r="E11" s="10">
+      <c r="E11" s="8">
         <v>126</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="8">
         <v>126</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="8">
         <v>1000</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>500</v>
       </c>
-      <c r="I11" s="10">
+      <c r="I11" s="8">
         <v>500</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="8">
         <v>0</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="8">
         <v>500</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="28.5">
-      <c r="A12" s="10">
+      <c r="A12" s="8">
         <v>11</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="8">
         <v>93</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="8">
         <v>92</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="8">
         <v>92</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="8">
         <v>523711</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <v>7500</v>
       </c>
-      <c r="I12" s="10">
+      <c r="I12" s="8">
         <v>7500</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J12" s="8">
         <v>5336</v>
       </c>
-      <c r="K12" s="10">
+      <c r="K12" s="8">
         <v>5800</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="9" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="10">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="8">
         <v>87</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="8">
         <v>87</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="8">
         <v>87</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="8">
         <v>2000</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>500</v>
       </c>
-      <c r="I13" s="10">
+      <c r="I13" s="8">
         <v>500</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J13" s="8">
         <v>0</v>
       </c>
-      <c r="K13" s="10">
+      <c r="K13" s="8">
         <v>500</v>
       </c>
-      <c r="L13" s="11" t="s">
+      <c r="L13" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="10">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="8">
         <v>77</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="8">
         <v>77</v>
       </c>
-      <c r="F14" s="10">
+      <c r="F14" s="8">
         <v>77</v>
       </c>
-      <c r="G14" s="10">
+      <c r="G14" s="8">
         <v>500</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <v>500</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="8">
         <v>500</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
-      <c r="K14" s="10">
+      <c r="K14" s="8">
         <v>500</v>
       </c>
-      <c r="L14" s="11" t="s">
+      <c r="L14" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="28.5">
-      <c r="A15" s="10">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="8">
         <v>77</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E15" s="8">
         <v>77</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="8">
         <v>77</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="8">
         <v>0</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>499</v>
       </c>
-      <c r="I15" s="10">
+      <c r="I15" s="8">
         <v>499</v>
       </c>
-      <c r="J15" s="10">
+      <c r="J15" s="8">
         <v>0</v>
       </c>
-      <c r="K15" s="10">
+      <c r="K15" s="8">
         <v>0</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="28.5">
-      <c r="A16" s="10">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="8">
         <v>77</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="8">
         <v>77</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="8">
         <v>77</v>
       </c>
-      <c r="G16" s="10">
+      <c r="G16" s="8">
         <v>21259</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="8">
         <v>490</v>
       </c>
-      <c r="I16" s="10">
+      <c r="I16" s="8">
         <v>490</v>
       </c>
-      <c r="J16" s="10">
+      <c r="J16" s="8">
         <v>0</v>
       </c>
-      <c r="K16" s="10">
+      <c r="K16" s="8">
         <v>290</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="28.5">
-      <c r="A17" s="10">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="8">
         <v>76</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="8">
         <v>73</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="8">
         <v>73</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="8">
         <v>94973</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>2070</v>
       </c>
-      <c r="I17" s="10">
+      <c r="I17" s="8">
         <v>2070</v>
       </c>
-      <c r="J17" s="10">
+      <c r="J17" s="8">
         <v>1161</v>
       </c>
-      <c r="K17" s="10">
+      <c r="K17" s="8">
         <v>1290</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="28.5">
-      <c r="A18" s="10">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18" s="8">
         <v>69</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="8">
         <v>61</v>
       </c>
-      <c r="F18" s="10">
+      <c r="F18" s="8">
         <v>61</v>
       </c>
-      <c r="G18" s="10">
+      <c r="G18" s="8">
         <v>114808</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>2760</v>
       </c>
-      <c r="I18" s="10">
+      <c r="I18" s="8">
         <v>2760</v>
       </c>
-      <c r="J18" s="10">
+      <c r="J18" s="8">
         <v>1554</v>
       </c>
-      <c r="K18" s="10">
+      <c r="K18" s="8">
         <v>1690</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="28.5">
-      <c r="A19" s="10">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19" s="8">
         <v>67</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="8">
         <v>67</v>
       </c>
-      <c r="F19" s="10">
+      <c r="F19" s="8">
         <v>67</v>
       </c>
-      <c r="G19" s="10">
+      <c r="G19" s="8">
         <v>179980</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>3580</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I19" s="8">
         <v>3580</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J19" s="8">
         <v>2555</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K19" s="8">
         <v>2690</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="10">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="8">
         <v>67</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="8">
         <v>64</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="8">
         <v>64</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="8">
         <v>6566</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>98</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I20" s="8">
         <v>98</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J20" s="8">
         <v>98</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K20" s="8">
         <v>98</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="10">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="8">
         <v>66</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="8">
         <v>66</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="8">
         <v>66</v>
       </c>
-      <c r="G21" s="10">
+      <c r="G21" s="8">
         <v>1470</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>98</v>
       </c>
-      <c r="I21" s="10">
+      <c r="I21" s="8">
         <v>98</v>
       </c>
-      <c r="J21" s="10">
+      <c r="J21" s="8">
         <v>0</v>
       </c>
-      <c r="K21" s="10">
+      <c r="K21" s="8">
         <v>98</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="9" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="28.5">
-      <c r="A22" s="10">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="8">
         <v>65</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="8">
         <v>59</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="8">
         <v>59</v>
       </c>
-      <c r="G22" s="10">
+      <c r="G22" s="8">
         <v>14930</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <v>290</v>
       </c>
-      <c r="I22" s="10">
+      <c r="I22" s="8">
         <v>290</v>
       </c>
-      <c r="J22" s="10">
+      <c r="J22" s="8">
         <v>225</v>
       </c>
-      <c r="K22" s="10">
+      <c r="K22" s="8">
         <v>230</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="9" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="28.5">
-      <c r="A23" s="10">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23" s="8">
         <v>63</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="8">
         <v>62</v>
       </c>
-      <c r="F23" s="10">
+      <c r="F23" s="8">
         <v>62</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="8">
         <v>477710</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>10000</v>
       </c>
-      <c r="I23" s="10">
+      <c r="I23" s="8">
         <v>10000</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="8">
         <v>7084</v>
       </c>
-      <c r="K23" s="10">
+      <c r="K23" s="8">
         <v>7700</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="28.5">
-      <c r="A24" s="10">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24" s="8">
         <v>61</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="8">
         <v>61</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="8">
         <v>61</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="8">
         <v>16820</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <v>490</v>
       </c>
-      <c r="I24" s="10">
+      <c r="I24" s="8">
         <v>490</v>
       </c>
-      <c r="J24" s="10">
+      <c r="J24" s="8">
         <v>0</v>
       </c>
-      <c r="K24" s="10">
+      <c r="K24" s="8">
         <v>290</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="10">
+      <c r="A25" s="8">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="8">
         <v>55</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="8">
         <v>51</v>
       </c>
-      <c r="F25" s="10">
+      <c r="F25" s="8">
         <v>51</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="8">
         <v>21450</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>690</v>
       </c>
-      <c r="I25" s="10">
+      <c r="I25" s="8">
         <v>690</v>
       </c>
-      <c r="J25" s="10">
+      <c r="J25" s="8">
         <v>390</v>
       </c>
-      <c r="K25" s="10">
+      <c r="K25" s="8">
         <v>390</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="9" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="10">
+      <c r="A26" s="8">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="8">
         <v>54</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="8">
         <v>54</v>
       </c>
-      <c r="F26" s="10">
+      <c r="F26" s="8">
         <v>54</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="8">
         <v>0</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <v>1000</v>
       </c>
-      <c r="I26" s="10">
+      <c r="I26" s="8">
         <v>1000</v>
       </c>
-      <c r="J26" s="10">
+      <c r="J26" s="8">
         <v>0</v>
       </c>
-      <c r="K26" s="10">
+      <c r="K26" s="8">
         <v>0</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="9" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="10">
+      <c r="A27" s="8">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="8">
         <v>49</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="8">
         <v>49</v>
       </c>
-      <c r="F27" s="10">
+      <c r="F27" s="8">
         <v>49</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="8">
         <v>0</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>500</v>
       </c>
-      <c r="I27" s="10">
+      <c r="I27" s="8">
         <v>500</v>
       </c>
-      <c r="J27" s="10">
+      <c r="J27" s="8">
         <v>0</v>
       </c>
-      <c r="K27" s="10">
+      <c r="K27" s="8">
         <v>0</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="10">
+      <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="8">
         <v>41</v>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="8">
         <v>41</v>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="8">
         <v>41</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="8">
         <v>20065</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <v>980</v>
       </c>
-      <c r="I28" s="10">
+      <c r="I28" s="8">
         <v>980</v>
       </c>
-      <c r="J28" s="10">
+      <c r="J28" s="8">
         <v>465</v>
       </c>
-      <c r="K28" s="10">
+      <c r="K28" s="8">
         <v>490</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="28.5">
-      <c r="A29" s="10">
+      <c r="A29" s="8">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="8">
         <v>38</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="8">
         <v>38</v>
       </c>
-      <c r="F29" s="10">
+      <c r="F29" s="8">
         <v>38</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="8">
         <v>56436</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <v>2370</v>
       </c>
-      <c r="I29" s="10">
+      <c r="I29" s="8">
         <v>2370</v>
       </c>
-      <c r="J29" s="10">
+      <c r="J29" s="8">
         <v>1444</v>
       </c>
-      <c r="K29" s="10">
+      <c r="K29" s="8">
         <v>1490</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="L29" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="28.5">
-      <c r="A30" s="10">
+      <c r="A30" s="8">
         <v>29</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="8">
         <v>33</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="8">
         <v>33</v>
       </c>
-      <c r="F30" s="10">
+      <c r="F30" s="8">
         <v>33</v>
       </c>
-      <c r="G30" s="10">
+      <c r="G30" s="8">
         <v>72600</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <v>2500</v>
       </c>
-      <c r="I30" s="10">
+      <c r="I30" s="8">
         <v>2500</v>
       </c>
-      <c r="J30" s="10">
+      <c r="J30" s="8">
         <v>2200</v>
       </c>
-      <c r="K30" s="10">
+      <c r="K30" s="8">
         <v>2200</v>
       </c>
-      <c r="L30" s="11" t="s">
+      <c r="L30" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="10">
+      <c r="A31" s="8">
         <v>30</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="8">
         <v>33</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="8">
         <v>33</v>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="8">
         <v>33</v>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="8">
         <v>14157</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <v>880</v>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="8">
         <v>880</v>
       </c>
-      <c r="J31" s="10">
+      <c r="J31" s="8">
         <v>429</v>
       </c>
-      <c r="K31" s="10">
+      <c r="K31" s="8">
         <v>429</v>
       </c>
-      <c r="L31" s="11" t="s">
+      <c r="L31" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="28.5">
-      <c r="A32" s="10">
+      <c r="A32" s="8">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="8">
         <v>27</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="8">
         <v>27</v>
       </c>
-      <c r="F32" s="10">
+      <c r="F32" s="8">
         <v>27</v>
       </c>
-      <c r="G32" s="10">
+      <c r="G32" s="8">
         <v>69930</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="8">
         <v>3190</v>
       </c>
-      <c r="I32" s="10">
+      <c r="I32" s="8">
         <v>3190</v>
       </c>
-      <c r="J32" s="10">
+      <c r="J32" s="8">
         <v>2590</v>
       </c>
-      <c r="K32" s="10">
+      <c r="K32" s="8">
         <v>2590</v>
       </c>
-      <c r="L32" s="11" t="s">
+      <c r="L32" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="10">
+      <c r="A33" s="8">
         <v>32</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33" s="8">
         <v>27</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="8">
         <v>27</v>
       </c>
-      <c r="F33" s="10">
+      <c r="F33" s="8">
         <v>27</v>
       </c>
-      <c r="G33" s="10">
+      <c r="G33" s="8">
         <v>11583</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <v>880</v>
       </c>
-      <c r="I33" s="10">
+      <c r="I33" s="8">
         <v>880</v>
       </c>
-      <c r="J33" s="10">
+      <c r="J33" s="8">
         <v>429</v>
       </c>
-      <c r="K33" s="10">
+      <c r="K33" s="8">
         <v>429</v>
       </c>
-      <c r="L33" s="11" t="s">
+      <c r="L33" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="28.5">
-      <c r="A34" s="10">
+      <c r="A34" s="8">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34" s="8">
         <v>23</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="8">
         <v>20</v>
       </c>
-      <c r="F34" s="10">
+      <c r="F34" s="8">
         <v>20</v>
       </c>
-      <c r="G34" s="10">
+      <c r="G34" s="8">
         <v>18170</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="8">
         <v>1560</v>
       </c>
-      <c r="I34" s="10">
+      <c r="I34" s="8">
         <v>1560</v>
       </c>
-      <c r="J34" s="10">
+      <c r="J34" s="8">
         <v>790</v>
       </c>
-      <c r="K34" s="10">
+      <c r="K34" s="8">
         <v>790</v>
       </c>
-      <c r="L34" s="11" t="s">
+      <c r="L34" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="28.5">
-      <c r="A35" s="10">
+      <c r="A35" s="8">
         <v>34</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35" s="8">
         <v>21</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="8">
         <v>21</v>
       </c>
-      <c r="F35" s="10">
+      <c r="F35" s="8">
         <v>21</v>
       </c>
-      <c r="G35" s="10">
+      <c r="G35" s="8">
         <v>13020</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="8">
         <v>1170</v>
       </c>
-      <c r="I35" s="10">
+      <c r="I35" s="8">
         <v>1170</v>
       </c>
-      <c r="J35" s="10">
+      <c r="J35" s="8">
         <v>620</v>
       </c>
-      <c r="K35" s="10">
+      <c r="K35" s="8">
         <v>620</v>
       </c>
-      <c r="L35" s="11" t="s">
+      <c r="L35" s="9" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="10">
+      <c r="A36" s="8">
         <v>35</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36" s="8">
         <v>13</v>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="8">
         <v>12</v>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="8">
         <v>12</v>
       </c>
-      <c r="G36" s="10">
+      <c r="G36" s="8">
         <v>12350</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="8">
         <v>2070</v>
       </c>
-      <c r="I36" s="10">
+      <c r="I36" s="8">
         <v>2070</v>
       </c>
-      <c r="J36" s="10">
+      <c r="J36" s="8">
         <v>950</v>
       </c>
-      <c r="K36" s="10">
+      <c r="K36" s="8">
         <v>950</v>
       </c>
-      <c r="L36" s="11" t="s">
+      <c r="L36" s="9" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="10">
+      <c r="A37" s="8">
         <v>36</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37" s="8">
         <v>9</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="8">
         <v>9</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F37" s="8">
         <v>9</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G37" s="8">
         <v>5757</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="8">
         <v>1180</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I37" s="8">
         <v>1180</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J37" s="8">
         <v>637</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K37" s="8">
         <v>640</v>
       </c>
-      <c r="L37" s="11" t="s">
+      <c r="L37" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="28.5">
-      <c r="A38" s="10">
+      <c r="A38" s="8">
         <v>37</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38" s="8">
         <v>9</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="8">
         <v>9</v>
       </c>
-      <c r="F38" s="10">
+      <c r="F38" s="8">
         <v>9</v>
       </c>
-      <c r="G38" s="10">
+      <c r="G38" s="8">
         <v>8910</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="8">
         <v>1290</v>
       </c>
-      <c r="I38" s="10">
+      <c r="I38" s="8">
         <v>1290</v>
       </c>
-      <c r="J38" s="10">
+      <c r="J38" s="8">
         <v>990</v>
       </c>
-      <c r="K38" s="10">
+      <c r="K38" s="8">
         <v>990</v>
       </c>
-      <c r="L38" s="11" t="s">
+      <c r="L38" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="10">
+      <c r="A39" s="8">
         <v>38</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39" s="8">
         <v>8</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="8">
         <v>7</v>
       </c>
-      <c r="F39" s="10">
+      <c r="F39" s="8">
         <v>7</v>
       </c>
-      <c r="G39" s="10">
+      <c r="G39" s="8">
         <v>3895</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="8">
         <v>980</v>
       </c>
-      <c r="I39" s="10">
+      <c r="I39" s="8">
         <v>980</v>
       </c>
-      <c r="J39" s="10">
+      <c r="J39" s="8">
         <v>465</v>
       </c>
-      <c r="K39" s="10">
+      <c r="K39" s="8">
         <v>490</v>
       </c>
-      <c r="L39" s="11" t="s">
+      <c r="L39" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="10">
+      <c r="A40" s="8">
         <v>39</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40" s="8">
         <v>6</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="8">
         <v>6</v>
       </c>
-      <c r="F40" s="10">
+      <c r="F40" s="8">
         <v>6</v>
       </c>
-      <c r="G40" s="10">
+      <c r="G40" s="8">
         <v>3840</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="8">
         <v>1180</v>
       </c>
-      <c r="I40" s="10">
+      <c r="I40" s="8">
         <v>1180</v>
       </c>
-      <c r="J40" s="10">
+      <c r="J40" s="8">
         <v>640</v>
       </c>
-      <c r="K40" s="10">
+      <c r="K40" s="8">
         <v>640</v>
       </c>
-      <c r="L40" s="11" t="s">
+      <c r="L40" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="10">
+      <c r="A41" s="8">
         <v>40</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41" s="8">
         <v>4</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="8">
         <v>4</v>
       </c>
-      <c r="F41" s="10">
+      <c r="F41" s="8">
         <v>4</v>
       </c>
-      <c r="G41" s="10">
+      <c r="G41" s="8">
         <v>4520</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="8">
         <v>1780</v>
       </c>
-      <c r="I41" s="10">
+      <c r="I41" s="8">
         <v>1780</v>
       </c>
-      <c r="J41" s="10">
+      <c r="J41" s="8">
         <v>1130</v>
       </c>
-      <c r="K41" s="10">
+      <c r="K41" s="8">
         <v>1130</v>
       </c>
-      <c r="L41" s="11" t="s">
+      <c r="L41" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="10">
+      <c r="A42" s="8">
         <v>41</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="8">
         <v>4</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="8">
         <v>3</v>
       </c>
-      <c r="F42" s="10">
+      <c r="F42" s="8">
         <v>3</v>
       </c>
-      <c r="G42" s="10">
+      <c r="G42" s="8">
         <v>1960</v>
       </c>
-      <c r="H42" s="10">
+      <c r="H42" s="8">
         <v>980</v>
       </c>
-      <c r="I42" s="10">
+      <c r="I42" s="8">
         <v>980</v>
       </c>
-      <c r="J42" s="10">
+      <c r="J42" s="8">
         <v>490</v>
       </c>
-      <c r="K42" s="10">
+      <c r="K42" s="8">
         <v>490</v>
       </c>
-      <c r="L42" s="11" t="s">
+      <c r="L42" s="9" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="10">
+      <c r="A43" s="8">
         <v>42</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="C43" s="10" t="s">
+      <c r="C43" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="8">
         <v>4</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="8">
         <v>4</v>
       </c>
-      <c r="F43" s="10">
+      <c r="F43" s="8">
         <v>4</v>
       </c>
-      <c r="G43" s="10">
+      <c r="G43" s="8">
         <v>3000</v>
       </c>
-      <c r="H43" s="10">
+      <c r="H43" s="8">
         <v>1580</v>
       </c>
-      <c r="I43" s="10">
+      <c r="I43" s="8">
         <v>1580</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J43" s="8">
         <v>750</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="8">
         <v>750</v>
       </c>
-      <c r="L43" s="11" t="s">
+      <c r="L43" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="10">
+      <c r="A44" s="8">
         <v>43</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44" s="8">
         <v>3</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="8">
         <v>3</v>
       </c>
-      <c r="F44" s="10">
+      <c r="F44" s="8">
         <v>3</v>
       </c>
-      <c r="G44" s="10">
+      <c r="G44" s="8">
         <v>3390</v>
       </c>
-      <c r="H44" s="10">
+      <c r="H44" s="8">
         <v>1780</v>
       </c>
-      <c r="I44" s="10">
+      <c r="I44" s="8">
         <v>1780</v>
       </c>
-      <c r="J44" s="10">
+      <c r="J44" s="8">
         <v>1130</v>
       </c>
-      <c r="K44" s="10">
+      <c r="K44" s="8">
         <v>1130</v>
       </c>
-      <c r="L44" s="11" t="s">
+      <c r="L44" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="28.5">
-      <c r="A45" s="10">
+      <c r="A45" s="8">
         <v>44</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="8">
         <v>2</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="8">
         <v>2</v>
       </c>
-      <c r="F45" s="10">
+      <c r="F45" s="8">
         <v>2</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="8">
         <v>4780</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="8">
         <v>2890</v>
       </c>
-      <c r="I45" s="10">
+      <c r="I45" s="8">
         <v>2890</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J45" s="8">
         <v>2390</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="8">
         <v>2390</v>
       </c>
-      <c r="L45" s="11" t="s">
+      <c r="L45" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="10">
+      <c r="A46" s="8">
         <v>45</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46" s="8">
         <v>2</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="8">
         <v>2</v>
       </c>
-      <c r="F46" s="10">
+      <c r="F46" s="8">
         <v>2</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="8">
         <v>1158</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="8">
         <v>1180</v>
       </c>
-      <c r="I46" s="10">
+      <c r="I46" s="8">
         <v>1180</v>
       </c>
-      <c r="J46" s="10">
+      <c r="J46" s="8">
         <v>579</v>
       </c>
-      <c r="K46" s="10">
+      <c r="K46" s="8">
         <v>579</v>
       </c>
-      <c r="L46" s="11" t="s">
+      <c r="L46" s="9" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="10">
+      <c r="A47" s="8">
         <v>46</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47" s="8">
         <v>2</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="8">
         <v>2</v>
       </c>
-      <c r="F47" s="10">
+      <c r="F47" s="8">
         <v>2</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="8">
         <v>1060</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="8">
         <v>1180</v>
       </c>
-      <c r="I47" s="10">
+      <c r="I47" s="8">
         <v>1180</v>
       </c>
-      <c r="J47" s="10">
+      <c r="J47" s="8">
         <v>530</v>
       </c>
-      <c r="K47" s="10">
+      <c r="K47" s="8">
         <v>530</v>
       </c>
-      <c r="L47" s="11" t="s">
+      <c r="L47" s="9" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="10">
+      <c r="A48" s="8">
         <v>47</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48" s="8">
         <v>2</v>
       </c>
-      <c r="E48" s="10">
+      <c r="E48" s="8">
         <v>2</v>
       </c>
-      <c r="F48" s="10">
+      <c r="F48" s="8">
         <v>2</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="8">
         <v>1458</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="8">
         <v>1380</v>
       </c>
-      <c r="I48" s="10">
+      <c r="I48" s="8">
         <v>1380</v>
       </c>
-      <c r="J48" s="10">
+      <c r="J48" s="8">
         <v>729</v>
       </c>
-      <c r="K48" s="10">
+      <c r="K48" s="8">
         <v>729</v>
       </c>
-      <c r="L48" s="11" t="s">
+      <c r="L48" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="10">
+      <c r="A49" s="8">
         <v>48</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49" s="8">
         <v>1</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="8">
         <v>1</v>
       </c>
-      <c r="F49" s="10">
+      <c r="F49" s="8">
         <v>1</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="8">
         <v>1190</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="8">
         <v>2560</v>
       </c>
-      <c r="I49" s="10">
+      <c r="I49" s="8">
         <v>2560</v>
       </c>
-      <c r="J49" s="10">
+      <c r="J49" s="8">
         <v>1190</v>
       </c>
-      <c r="K49" s="10">
+      <c r="K49" s="8">
         <v>1190</v>
       </c>
-      <c r="L49" s="11" t="s">
+      <c r="L49" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="10">
+      <c r="A50" s="8">
         <v>49</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50" s="8">
         <v>1</v>
       </c>
-      <c r="E50" s="10">
+      <c r="E50" s="8">
         <v>1</v>
       </c>
-      <c r="F50" s="10">
+      <c r="F50" s="8">
         <v>1</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="8">
         <v>1190</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="8">
         <v>2560</v>
       </c>
-      <c r="I50" s="10">
+      <c r="I50" s="8">
         <v>2560</v>
       </c>
-      <c r="J50" s="10">
+      <c r="J50" s="8">
         <v>1190</v>
       </c>
-      <c r="K50" s="10">
+      <c r="K50" s="8">
         <v>1190</v>
       </c>
-      <c r="L50" s="11" t="s">
+      <c r="L50" s="9" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="10">
+      <c r="A51" s="8">
         <v>50</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="8">
         <v>1</v>
       </c>
-      <c r="E51" s="10">
+      <c r="E51" s="8">
         <v>1</v>
       </c>
-      <c r="F51" s="10">
+      <c r="F51" s="8">
         <v>1</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="8">
         <v>3190</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="8">
         <v>5460</v>
       </c>
-      <c r="I51" s="10">
+      <c r="I51" s="8">
         <v>5460</v>
       </c>
-      <c r="J51" s="10">
+      <c r="J51" s="8">
         <v>3190</v>
       </c>
-      <c r="K51" s="10">
+      <c r="K51" s="8">
         <v>3190</v>
       </c>
-      <c r="L51" s="11" t="s">
+      <c r="L51" s="9" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="10">
+      <c r="A52" s="8">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52" s="8">
         <v>1</v>
       </c>
-      <c r="E52" s="10">
+      <c r="E52" s="8">
         <v>1</v>
       </c>
-      <c r="F52" s="10">
+      <c r="F52" s="8">
         <v>1</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="8">
         <v>3190</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="8">
         <v>5460</v>
       </c>
-      <c r="I52" s="10">
+      <c r="I52" s="8">
         <v>5460</v>
       </c>
-      <c r="J52" s="10">
+      <c r="J52" s="8">
         <v>3190</v>
       </c>
-      <c r="K52" s="10">
+      <c r="K52" s="8">
         <v>3190</v>
       </c>
-      <c r="L52" s="11" t="s">
+      <c r="L52" s="9" t="s">
         <v>147</v>
       </c>
     </row>
